--- a/backend/data/financials_by_company/1MC.AX.xlsx
+++ b/backend/data/financials_by_company/1MC.AX.xlsx
@@ -637,7 +637,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -646,391 +646,389 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-2625866</v>
+        <v>-13088123</v>
       </c>
       <c r="E2" t="n">
-        <v>-2953585</v>
+        <v>-13034710</v>
       </c>
       <c r="F2" t="n">
-        <v>133921</v>
+        <v>67309</v>
       </c>
       <c r="G2" t="n">
-        <v>435134</v>
+        <v>424091</v>
       </c>
       <c r="H2" t="n">
-        <v>-2625866</v>
+        <v>-13088123</v>
       </c>
       <c r="I2" t="n">
-        <v>-2759787</v>
+        <v>-13155432</v>
       </c>
       <c r="J2" t="n">
-        <v>-240190</v>
+        <v>-77008</v>
       </c>
       <c r="K2" t="n">
-        <v>240190</v>
+        <v>77008</v>
       </c>
       <c r="L2" t="n">
-        <v>-2953585</v>
+        <v>-13034710</v>
       </c>
       <c r="M2" t="n">
-        <v>-2901986</v>
+        <v>-72802486</v>
       </c>
       <c r="N2" t="n">
-        <v>246272793</v>
+        <v>132390078</v>
       </c>
       <c r="O2" t="n">
-        <v>246272793</v>
+        <v>132390078</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0125</v>
+        <v>-0.550376</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0125</v>
+        <v>-0.550376</v>
       </c>
       <c r="R2" t="n">
-        <v>-2901986</v>
+        <v>-72802486</v>
       </c>
       <c r="S2" t="n">
-        <v>-2901986</v>
+        <v>-72802486</v>
       </c>
       <c r="T2" t="n">
-        <v>46392</v>
+        <v>197730</v>
       </c>
       <c r="U2" t="n">
-        <v>-2948378</v>
+        <v>-73000216</v>
       </c>
       <c r="V2" t="n">
-        <v>51599</v>
+        <v>-59767776</v>
       </c>
       <c r="W2" t="n">
-        <v>-2999977</v>
+        <v>-13232440</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2999977</v>
+        <v>-13232440</v>
       </c>
       <c r="Z2" t="n">
-        <v>-74487</v>
+        <v>-5914099</v>
       </c>
       <c r="AA2" t="n">
-        <v>-74487</v>
+        <v>-5914099</v>
       </c>
       <c r="AB2" t="n">
-        <v>-240190</v>
+        <v>-77008</v>
       </c>
       <c r="AC2" t="n">
-        <v>240190</v>
+        <v>77008</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2685300</v>
+        <v>-7241333</v>
       </c>
       <c r="AE2" t="n">
-        <v>2776366</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-30</v>
-      </c>
+        <v>6950624</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>133921</v>
+        <v>67309</v>
       </c>
       <c r="AH2" t="n">
-        <v>133921</v>
+        <v>67309</v>
       </c>
       <c r="AI2" t="n">
-        <v>133921</v>
+        <v>67309</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2642475</v>
+        <v>6883315</v>
       </c>
       <c r="AK2" t="n">
-        <v>2642475</v>
+        <v>6883315</v>
       </c>
       <c r="AL2" t="n">
-        <v>378699</v>
+        <v>4427189</v>
       </c>
       <c r="AM2" t="n">
-        <v>2263776</v>
+        <v>2456126</v>
       </c>
       <c r="AN2" t="n">
-        <v>91066</v>
+        <v>-290709</v>
       </c>
       <c r="AO2" t="n">
-        <v>435134</v>
+        <v>424091</v>
       </c>
       <c r="AP2" t="n">
-        <v>526200</v>
+        <v>133382</v>
       </c>
       <c r="AQ2" t="n">
-        <v>526200</v>
+        <v>133382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.019993</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-2358660</v>
+        <v>219081</v>
       </c>
       <c r="E3" t="n">
-        <v>-2542777</v>
+        <v>-97866</v>
       </c>
       <c r="F3" t="n">
-        <v>60012</v>
+        <v>44068</v>
       </c>
       <c r="G3" t="n">
-        <v>403698</v>
+        <v>483026</v>
       </c>
       <c r="H3" t="n">
-        <v>-2358660</v>
+        <v>219081</v>
       </c>
       <c r="I3" t="n">
-        <v>-2418672</v>
+        <v>175013</v>
       </c>
       <c r="J3" t="n">
-        <v>-241438</v>
+        <v>-274859</v>
       </c>
       <c r="K3" t="n">
-        <v>241438</v>
+        <v>274859</v>
       </c>
       <c r="L3" t="n">
-        <v>-2542777</v>
+        <v>-97866</v>
       </c>
       <c r="M3" t="n">
-        <v>-2845183</v>
+        <v>-681014</v>
       </c>
       <c r="N3" t="n">
-        <v>235709783</v>
+        <v>170600704</v>
       </c>
       <c r="O3" t="n">
-        <v>235709783</v>
+        <v>170600704</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0125</v>
+        <v>-0.005</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0125</v>
+        <v>-0.005</v>
       </c>
       <c r="R3" t="n">
-        <v>-2845183</v>
+        <v>-681014</v>
       </c>
       <c r="S3" t="n">
-        <v>-2845183</v>
+        <v>-681014</v>
       </c>
       <c r="T3" t="n">
-        <v>64150</v>
+        <v>1980</v>
       </c>
       <c r="U3" t="n">
-        <v>-2909333</v>
+        <v>-682994</v>
       </c>
       <c r="V3" t="n">
-        <v>-302406</v>
+        <v>-583148</v>
       </c>
       <c r="W3" t="n">
-        <v>-2606927</v>
+        <v>-99846</v>
       </c>
       <c r="X3" t="n">
-        <v>-53183</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2660110</v>
+        <v>-99846</v>
       </c>
       <c r="Z3" t="n">
-        <v>4219951</v>
+        <v>6536199</v>
       </c>
       <c r="AA3" t="n">
-        <v>4219951</v>
+        <v>6536199</v>
       </c>
       <c r="AB3" t="n">
-        <v>-241438</v>
+        <v>-274859</v>
       </c>
       <c r="AC3" t="n">
-        <v>241438</v>
+        <v>274859</v>
       </c>
       <c r="AD3" t="n">
-        <v>-6638623</v>
+        <v>-6361186</v>
       </c>
       <c r="AE3" t="n">
-        <v>6714655</v>
+        <v>6167097</v>
       </c>
       <c r="AF3" t="n">
-        <v>92358</v>
+        <v>46280</v>
       </c>
       <c r="AG3" t="n">
-        <v>60012</v>
+        <v>44068</v>
       </c>
       <c r="AH3" t="n">
-        <v>60012</v>
+        <v>44068</v>
       </c>
       <c r="AI3" t="n">
-        <v>60012</v>
+        <v>44068</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6562285</v>
+        <v>6076749</v>
       </c>
       <c r="AK3" t="n">
-        <v>6562285</v>
+        <v>6076749</v>
       </c>
       <c r="AL3" t="n">
-        <v>775577</v>
+        <v>4444414</v>
       </c>
       <c r="AM3" t="n">
-        <v>5786708</v>
+        <v>1632335</v>
       </c>
       <c r="AN3" t="n">
-        <v>76032</v>
+        <v>-194089</v>
       </c>
       <c r="AO3" t="n">
-        <v>403698</v>
+        <v>483026</v>
       </c>
       <c r="AP3" t="n">
-        <v>479730</v>
+        <v>288937</v>
       </c>
       <c r="AQ3" t="n">
-        <v>479730</v>
+        <v>288937</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.019993</v>
       </c>
       <c r="D4" t="n">
-        <v>219081</v>
+        <v>-2358660</v>
       </c>
       <c r="E4" t="n">
-        <v>-97866</v>
+        <v>-2542777</v>
       </c>
       <c r="F4" t="n">
-        <v>44068</v>
+        <v>60012</v>
       </c>
       <c r="G4" t="n">
-        <v>483026</v>
+        <v>403698</v>
       </c>
       <c r="H4" t="n">
-        <v>219081</v>
+        <v>-2358660</v>
       </c>
       <c r="I4" t="n">
-        <v>175013</v>
+        <v>-2418672</v>
       </c>
       <c r="J4" t="n">
-        <v>-274859</v>
+        <v>-241438</v>
       </c>
       <c r="K4" t="n">
-        <v>274859</v>
+        <v>241438</v>
       </c>
       <c r="L4" t="n">
-        <v>-97866</v>
+        <v>-2542777</v>
       </c>
       <c r="M4" t="n">
-        <v>-681014</v>
+        <v>-2845183</v>
       </c>
       <c r="N4" t="n">
-        <v>170600704</v>
+        <v>235709783</v>
       </c>
       <c r="O4" t="n">
-        <v>170600704</v>
+        <v>235709783</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.005</v>
+        <v>-0.0125</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.005</v>
+        <v>-0.0125</v>
       </c>
       <c r="R4" t="n">
-        <v>-681014</v>
+        <v>-2845183</v>
       </c>
       <c r="S4" t="n">
-        <v>-681014</v>
+        <v>-2845183</v>
       </c>
       <c r="T4" t="n">
-        <v>1980</v>
+        <v>64150</v>
       </c>
       <c r="U4" t="n">
-        <v>-682994</v>
+        <v>-2909333</v>
       </c>
       <c r="V4" t="n">
-        <v>-583148</v>
+        <v>-302406</v>
       </c>
       <c r="W4" t="n">
-        <v>-99846</v>
+        <v>-2606927</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-53183</v>
       </c>
       <c r="Y4" t="n">
-        <v>-99846</v>
+        <v>-2660110</v>
       </c>
       <c r="Z4" t="n">
-        <v>6536199</v>
+        <v>4219951</v>
       </c>
       <c r="AA4" t="n">
-        <v>6536199</v>
+        <v>4219951</v>
       </c>
       <c r="AB4" t="n">
-        <v>-274859</v>
+        <v>-241438</v>
       </c>
       <c r="AC4" t="n">
-        <v>274859</v>
+        <v>241438</v>
       </c>
       <c r="AD4" t="n">
-        <v>-6361186</v>
+        <v>-6638623</v>
       </c>
       <c r="AE4" t="n">
-        <v>6167097</v>
+        <v>6714655</v>
       </c>
       <c r="AF4" t="n">
-        <v>46280</v>
+        <v>92358</v>
       </c>
       <c r="AG4" t="n">
-        <v>44068</v>
+        <v>60012</v>
       </c>
       <c r="AH4" t="n">
-        <v>44068</v>
+        <v>60012</v>
       </c>
       <c r="AI4" t="n">
-        <v>44068</v>
+        <v>60012</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6076749</v>
+        <v>6562285</v>
       </c>
       <c r="AK4" t="n">
-        <v>6076749</v>
+        <v>6562285</v>
       </c>
       <c r="AL4" t="n">
-        <v>4444414</v>
+        <v>775577</v>
       </c>
       <c r="AM4" t="n">
-        <v>1632335</v>
+        <v>5786708</v>
       </c>
       <c r="AN4" t="n">
-        <v>-194089</v>
+        <v>76032</v>
       </c>
       <c r="AO4" t="n">
-        <v>483026</v>
+        <v>403698</v>
       </c>
       <c r="AP4" t="n">
-        <v>288937</v>
+        <v>479730</v>
       </c>
       <c r="AQ4" t="n">
-        <v>288937</v>
+        <v>479730</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -1039,122 +1037,124 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-13088123</v>
+        <v>-2625866</v>
       </c>
       <c r="E5" t="n">
-        <v>-13034710</v>
+        <v>-2953585</v>
       </c>
       <c r="F5" t="n">
-        <v>67309</v>
+        <v>133921</v>
       </c>
       <c r="G5" t="n">
-        <v>424091</v>
+        <v>435134</v>
       </c>
       <c r="H5" t="n">
-        <v>-13088123</v>
+        <v>-2625866</v>
       </c>
       <c r="I5" t="n">
-        <v>-13155432</v>
+        <v>-2759787</v>
       </c>
       <c r="J5" t="n">
-        <v>-77008</v>
+        <v>-240190</v>
       </c>
       <c r="K5" t="n">
-        <v>77008</v>
+        <v>240190</v>
       </c>
       <c r="L5" t="n">
-        <v>-13034710</v>
+        <v>-2953585</v>
       </c>
       <c r="M5" t="n">
-        <v>-72802486</v>
+        <v>-2901986</v>
       </c>
       <c r="N5" t="n">
-        <v>132390078</v>
+        <v>246272793</v>
       </c>
       <c r="O5" t="n">
-        <v>132390078</v>
+        <v>246272793</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.550376</v>
+        <v>-0.0125</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.550376</v>
+        <v>-0.0125</v>
       </c>
       <c r="R5" t="n">
-        <v>-72802486</v>
+        <v>-2901986</v>
       </c>
       <c r="S5" t="n">
-        <v>-72802486</v>
+        <v>-2901986</v>
       </c>
       <c r="T5" t="n">
-        <v>197730</v>
+        <v>46392</v>
       </c>
       <c r="U5" t="n">
-        <v>-73000216</v>
+        <v>-2948378</v>
       </c>
       <c r="V5" t="n">
-        <v>-59767776</v>
+        <v>51599</v>
       </c>
       <c r="W5" t="n">
-        <v>-13232440</v>
+        <v>-2999977</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-13232440</v>
+        <v>-2999977</v>
       </c>
       <c r="Z5" t="n">
-        <v>-5914099</v>
+        <v>-74487</v>
       </c>
       <c r="AA5" t="n">
-        <v>-5914099</v>
+        <v>-74487</v>
       </c>
       <c r="AB5" t="n">
-        <v>-77008</v>
+        <v>-240190</v>
       </c>
       <c r="AC5" t="n">
-        <v>77008</v>
+        <v>240190</v>
       </c>
       <c r="AD5" t="n">
-        <v>-7241333</v>
+        <v>-2685300</v>
       </c>
       <c r="AE5" t="n">
-        <v>6950624</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>2776366</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-30</v>
+      </c>
       <c r="AG5" t="n">
-        <v>67309</v>
+        <v>133921</v>
       </c>
       <c r="AH5" t="n">
-        <v>67309</v>
+        <v>133921</v>
       </c>
       <c r="AI5" t="n">
-        <v>67309</v>
+        <v>133921</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6883315</v>
+        <v>2642475</v>
       </c>
       <c r="AK5" t="n">
-        <v>6883315</v>
+        <v>2642475</v>
       </c>
       <c r="AL5" t="n">
-        <v>4427189</v>
+        <v>378699</v>
       </c>
       <c r="AM5" t="n">
-        <v>2456126</v>
+        <v>2263776</v>
       </c>
       <c r="AN5" t="n">
-        <v>-290709</v>
+        <v>91066</v>
       </c>
       <c r="AO5" t="n">
-        <v>424091</v>
+        <v>435134</v>
       </c>
       <c r="AP5" t="n">
-        <v>133382</v>
+        <v>526200</v>
       </c>
       <c r="AQ5" t="n">
-        <v>133382</v>
+        <v>526200</v>
       </c>
     </row>
   </sheetData>
@@ -1475,680 +1475,680 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>247151977</v>
+        <v>132390078</v>
       </c>
       <c r="C2" t="n">
-        <v>247151977</v>
+        <v>132390078</v>
       </c>
       <c r="D2" t="n">
-        <v>3099204</v>
+        <v>3167039</v>
       </c>
       <c r="E2" t="n">
-        <v>3534145</v>
+        <v>3539458</v>
       </c>
       <c r="F2" t="n">
-        <v>7810546</v>
+        <v>491372</v>
       </c>
       <c r="G2" t="n">
-        <v>11330570</v>
+        <v>4030830</v>
       </c>
       <c r="H2" t="n">
-        <v>934264</v>
+        <v>628296</v>
       </c>
       <c r="I2" t="n">
-        <v>7810546</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14121</v>
-      </c>
+        <v>491372</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>7810546</v>
+        <v>491372</v>
       </c>
       <c r="L2" t="n">
-        <v>11231474</v>
+        <v>491372</v>
       </c>
       <c r="M2" t="n">
-        <v>8234692</v>
+        <v>737316</v>
       </c>
       <c r="N2" t="n">
-        <v>424146</v>
+        <v>245944</v>
       </c>
       <c r="O2" t="n">
-        <v>7810546</v>
+        <v>491372</v>
       </c>
       <c r="P2" t="n">
-        <v>-6864954</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>6174940</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1601318</v>
+      </c>
       <c r="R2" t="n">
-        <v>525126</v>
+        <v>5161501</v>
       </c>
       <c r="S2" t="n">
-        <v>-7390080</v>
+        <v>-587879</v>
       </c>
       <c r="T2" t="n">
-        <v>-301591817</v>
+        <v>-296543867</v>
       </c>
       <c r="U2" t="n">
-        <v>316267317</v>
+        <v>290860299</v>
       </c>
       <c r="V2" t="n">
-        <v>316267317</v>
+        <v>290860299</v>
       </c>
       <c r="W2" t="n">
-        <v>4636029</v>
+        <v>6501464</v>
       </c>
       <c r="X2" t="n">
-        <v>3915916</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>494988</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>494988</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3420928</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>3420928</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>720113</v>
+        <v>6501464</v>
       </c>
       <c r="AE2" t="n">
-        <v>113217</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>14121</v>
-      </c>
+        <v>3539458</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>99096</v>
+        <v>3539458</v>
       </c>
       <c r="AH2" t="n">
-        <v>99096</v>
+        <v>3539458</v>
       </c>
       <c r="AI2" t="n">
-        <v>258599</v>
+        <v>489533</v>
       </c>
       <c r="AJ2" t="n">
-        <v>348297</v>
+        <v>2472473</v>
       </c>
       <c r="AK2" t="n">
-        <v>348297</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>2472473</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>77008</v>
+      </c>
       <c r="AM2" t="n">
-        <v>348297</v>
+        <v>2395465</v>
       </c>
       <c r="AN2" t="n">
-        <v>12870721</v>
+        <v>7238780</v>
       </c>
       <c r="AO2" t="n">
-        <v>11216344</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>445934</v>
-      </c>
+        <v>109020</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>10770411</v>
+        <v>109020</v>
       </c>
       <c r="AS2" t="n">
-        <v>-982911</v>
+        <v>-835149</v>
       </c>
       <c r="AT2" t="n">
-        <v>11753322</v>
+        <v>944169</v>
       </c>
       <c r="AU2" t="n">
-        <v>10743380</v>
+        <v>79947</v>
       </c>
       <c r="AV2" t="n">
-        <v>1009942</v>
+        <v>864222</v>
       </c>
       <c r="AW2" t="n">
-        <v>1654377</v>
+        <v>7129760</v>
       </c>
       <c r="AX2" t="n">
-        <v>86380</v>
+        <v>34185</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>96831</v>
+        <v>63817</v>
       </c>
       <c r="BA2" t="n">
-        <v>96831</v>
+        <v>63817</v>
       </c>
       <c r="BB2" t="n">
-        <v>131170</v>
+        <v>168308</v>
       </c>
       <c r="BC2" t="n">
-        <v>247364</v>
+        <v>799358</v>
       </c>
       <c r="BD2" t="n">
-        <v>-580102</v>
+        <v>-357355</v>
       </c>
       <c r="BE2" t="n">
-        <v>827466</v>
+        <v>1156713</v>
       </c>
       <c r="BF2" t="n">
-        <v>1092632</v>
+        <v>6064092</v>
       </c>
       <c r="BG2" t="n">
-        <v>671812</v>
+        <v>5691673</v>
       </c>
       <c r="BH2" t="n">
-        <v>420820</v>
+        <v>372419</v>
       </c>
       <c r="BI2" t="n">
-        <v>420820</v>
+        <v>372419</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>243943217</v>
+        <v>207048559</v>
       </c>
       <c r="C3" t="n">
-        <v>243943217</v>
+        <v>207048559</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3388635</v>
+        <v>3352946</v>
       </c>
       <c r="F3" t="n">
-        <v>11178786</v>
+        <v>2686973</v>
       </c>
       <c r="G3" t="n">
-        <v>14555646</v>
+        <v>6000523</v>
       </c>
       <c r="H3" t="n">
-        <v>8551709</v>
+        <v>3119674</v>
       </c>
       <c r="I3" t="n">
-        <v>11178786</v>
+        <v>2686973</v>
       </c>
       <c r="J3" t="n">
+        <v>39396</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5099778</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5099778</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2961697</v>
+      </c>
+      <c r="N3" t="n">
+        <v>274724</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5099778</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-451487</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1961318</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2806848</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-5219653</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-297224882</v>
+      </c>
+      <c r="U3" t="n">
+        <v>302776147</v>
+      </c>
+      <c r="V3" t="n">
+        <v>302776147</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4817480</v>
+      </c>
+      <c r="X3" t="n">
         <v>11775</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11178786</v>
-      </c>
-      <c r="L3" t="n">
-        <v>14555646</v>
-      </c>
-      <c r="M3" t="n">
-        <v>11541947</v>
-      </c>
-      <c r="N3" t="n">
-        <v>363161</v>
-      </c>
-      <c r="O3" t="n">
-        <v>11178786</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-5945578</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
-        <v>1413488</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-7359066</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-298597046</v>
-      </c>
-      <c r="U3" t="n">
-        <v>315721410</v>
-      </c>
-      <c r="V3" t="n">
-        <v>315721410</v>
-      </c>
-      <c r="W3" t="n">
-        <v>5285786</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3376860</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>3376860</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
-        <v>3376860</v>
-      </c>
+        <v>11775</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>11775</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>1908926</v>
+        <v>4805705</v>
       </c>
       <c r="AE3" t="n">
-        <v>11775</v>
+        <v>3341171</v>
       </c>
       <c r="AF3" t="n">
-        <v>11775</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+        <v>27621</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3313550</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3313550</v>
+      </c>
       <c r="AI3" t="n">
-        <v>752115</v>
+        <v>716587</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1145036</v>
+        <v>747947</v>
       </c>
       <c r="AK3" t="n">
-        <v>1145036</v>
+        <v>747947</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>1145036</v>
+        <v>747947</v>
       </c>
       <c r="AN3" t="n">
-        <v>16827733</v>
+        <v>10191982</v>
       </c>
       <c r="AO3" t="n">
-        <v>6367098</v>
+        <v>2244285</v>
       </c>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>6367098</v>
+        <v>2266603</v>
       </c>
       <c r="AS3" t="n">
-        <v>-909388</v>
+        <v>-840227</v>
       </c>
       <c r="AT3" t="n">
-        <v>7276486</v>
+        <v>3084512</v>
       </c>
       <c r="AU3" t="n">
-        <v>6344454</v>
+        <v>2252402</v>
       </c>
       <c r="AV3" t="n">
-        <v>932032</v>
+        <v>854428</v>
       </c>
       <c r="AW3" t="n">
-        <v>10460635</v>
+        <v>7925379</v>
       </c>
       <c r="AX3" t="n">
-        <v>86301</v>
+        <v>37309</v>
       </c>
       <c r="AY3" t="n">
-        <v>443201</v>
+        <v>329789</v>
       </c>
       <c r="AZ3" t="n">
-        <v>85419</v>
+        <v>74816</v>
       </c>
       <c r="BA3" t="n">
-        <v>85419</v>
+        <v>74816</v>
       </c>
       <c r="BB3" t="n">
-        <v>128957</v>
+        <v>49184</v>
       </c>
       <c r="BC3" t="n">
-        <v>253681</v>
+        <v>251613</v>
       </c>
       <c r="BD3" t="n">
-        <v>-599669</v>
+        <v>-575456</v>
       </c>
       <c r="BE3" t="n">
-        <v>853350</v>
+        <v>827069</v>
       </c>
       <c r="BF3" t="n">
-        <v>9463076</v>
+        <v>7182668</v>
       </c>
       <c r="BG3" t="n">
-        <v>1535993</v>
+        <v>2929303</v>
       </c>
       <c r="BH3" t="n">
-        <v>7927083</v>
+        <v>4253365</v>
       </c>
       <c r="BI3" t="n">
-        <v>7927083</v>
+        <v>4253365</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>207048559</v>
+        <v>243943217</v>
       </c>
       <c r="C4" t="n">
-        <v>207048559</v>
+        <v>243943217</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3352946</v>
+        <v>3388635</v>
       </c>
       <c r="F4" t="n">
-        <v>2686973</v>
+        <v>11178786</v>
       </c>
       <c r="G4" t="n">
-        <v>6000523</v>
+        <v>14555646</v>
       </c>
       <c r="H4" t="n">
-        <v>3119674</v>
+        <v>8551709</v>
       </c>
       <c r="I4" t="n">
-        <v>2686973</v>
+        <v>11178786</v>
       </c>
       <c r="J4" t="n">
-        <v>39396</v>
+        <v>11775</v>
       </c>
       <c r="K4" t="n">
-        <v>5099778</v>
+        <v>11178786</v>
       </c>
       <c r="L4" t="n">
-        <v>5099778</v>
+        <v>14555646</v>
       </c>
       <c r="M4" t="n">
-        <v>2961697</v>
+        <v>11541947</v>
       </c>
       <c r="N4" t="n">
-        <v>274724</v>
+        <v>363161</v>
       </c>
       <c r="O4" t="n">
-        <v>5099778</v>
+        <v>11178786</v>
       </c>
       <c r="P4" t="n">
-        <v>-451487</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1961318</v>
-      </c>
+        <v>-5945578</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>2806848</v>
+        <v>1413488</v>
       </c>
       <c r="S4" t="n">
-        <v>-5219653</v>
+        <v>-7359066</v>
       </c>
       <c r="T4" t="n">
-        <v>-297224882</v>
+        <v>-298597046</v>
       </c>
       <c r="U4" t="n">
-        <v>302776147</v>
+        <v>315721410</v>
       </c>
       <c r="V4" t="n">
-        <v>302776147</v>
+        <v>315721410</v>
       </c>
       <c r="W4" t="n">
-        <v>4817480</v>
+        <v>5285786</v>
       </c>
       <c r="X4" t="n">
-        <v>11775</v>
+        <v>3376860</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
+        <v>3376860</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>3376860</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1908926</v>
+      </c>
+      <c r="AE4" t="n">
         <v>11775</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AF4" t="n">
         <v>11775</v>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>4805705</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3341171</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>27621</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3313550</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3313550</v>
-      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>716587</v>
+        <v>752115</v>
       </c>
       <c r="AJ4" t="n">
-        <v>747947</v>
+        <v>1145036</v>
       </c>
       <c r="AK4" t="n">
-        <v>747947</v>
+        <v>1145036</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>747947</v>
+        <v>1145036</v>
       </c>
       <c r="AN4" t="n">
-        <v>10191982</v>
+        <v>16827733</v>
       </c>
       <c r="AO4" t="n">
-        <v>2244285</v>
+        <v>6367098</v>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>2266603</v>
+        <v>6367098</v>
       </c>
       <c r="AS4" t="n">
-        <v>-840227</v>
+        <v>-909388</v>
       </c>
       <c r="AT4" t="n">
-        <v>3084512</v>
+        <v>7276486</v>
       </c>
       <c r="AU4" t="n">
-        <v>2252402</v>
+        <v>6344454</v>
       </c>
       <c r="AV4" t="n">
-        <v>854428</v>
+        <v>932032</v>
       </c>
       <c r="AW4" t="n">
-        <v>7925379</v>
+        <v>10460635</v>
       </c>
       <c r="AX4" t="n">
-        <v>37309</v>
+        <v>86301</v>
       </c>
       <c r="AY4" t="n">
-        <v>329789</v>
+        <v>443201</v>
       </c>
       <c r="AZ4" t="n">
-        <v>74816</v>
+        <v>85419</v>
       </c>
       <c r="BA4" t="n">
-        <v>74816</v>
+        <v>85419</v>
       </c>
       <c r="BB4" t="n">
-        <v>49184</v>
+        <v>128957</v>
       </c>
       <c r="BC4" t="n">
-        <v>251613</v>
+        <v>253681</v>
       </c>
       <c r="BD4" t="n">
-        <v>-575456</v>
+        <v>-599669</v>
       </c>
       <c r="BE4" t="n">
-        <v>827069</v>
+        <v>853350</v>
       </c>
       <c r="BF4" t="n">
-        <v>7182668</v>
+        <v>9463076</v>
       </c>
       <c r="BG4" t="n">
-        <v>2929303</v>
+        <v>1535993</v>
       </c>
       <c r="BH4" t="n">
-        <v>4253365</v>
+        <v>7927083</v>
       </c>
       <c r="BI4" t="n">
-        <v>4253365</v>
+        <v>7927083</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>132390078</v>
+        <v>247151977</v>
       </c>
       <c r="C5" t="n">
-        <v>132390078</v>
+        <v>247151977</v>
       </c>
       <c r="D5" t="n">
-        <v>3167039</v>
+        <v>3099204</v>
       </c>
       <c r="E5" t="n">
-        <v>3539458</v>
+        <v>3534145</v>
       </c>
       <c r="F5" t="n">
-        <v>491372</v>
+        <v>7810546</v>
       </c>
       <c r="G5" t="n">
-        <v>4030830</v>
+        <v>11330570</v>
       </c>
       <c r="H5" t="n">
-        <v>628296</v>
+        <v>934264</v>
       </c>
       <c r="I5" t="n">
-        <v>491372</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>7810546</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14121</v>
+      </c>
       <c r="K5" t="n">
-        <v>491372</v>
+        <v>7810546</v>
       </c>
       <c r="L5" t="n">
-        <v>491372</v>
+        <v>11231474</v>
       </c>
       <c r="M5" t="n">
-        <v>737316</v>
+        <v>8234692</v>
       </c>
       <c r="N5" t="n">
-        <v>245944</v>
+        <v>424146</v>
       </c>
       <c r="O5" t="n">
-        <v>491372</v>
+        <v>7810546</v>
       </c>
       <c r="P5" t="n">
-        <v>6174940</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1601318</v>
-      </c>
+        <v>-6864954</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>5161501</v>
+        <v>525126</v>
       </c>
       <c r="S5" t="n">
-        <v>-587879</v>
+        <v>-7390080</v>
       </c>
       <c r="T5" t="n">
-        <v>-296543867</v>
+        <v>-301591817</v>
       </c>
       <c r="U5" t="n">
-        <v>290860299</v>
+        <v>316267317</v>
       </c>
       <c r="V5" t="n">
-        <v>290860299</v>
+        <v>316267317</v>
       </c>
       <c r="W5" t="n">
-        <v>6501464</v>
+        <v>4636029</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+        <v>3915916</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>494988</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>494988</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3420928</v>
+      </c>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>3420928</v>
+      </c>
       <c r="AD5" t="n">
-        <v>6501464</v>
+        <v>720113</v>
       </c>
       <c r="AE5" t="n">
-        <v>3539458</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>113217</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14121</v>
+      </c>
       <c r="AG5" t="n">
-        <v>3539458</v>
+        <v>99096</v>
       </c>
       <c r="AH5" t="n">
-        <v>3539458</v>
+        <v>99096</v>
       </c>
       <c r="AI5" t="n">
-        <v>489533</v>
+        <v>258599</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2472473</v>
+        <v>348297</v>
       </c>
       <c r="AK5" t="n">
-        <v>2472473</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>77008</v>
-      </c>
+        <v>348297</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>2395465</v>
+        <v>348297</v>
       </c>
       <c r="AN5" t="n">
-        <v>7238780</v>
+        <v>12870721</v>
       </c>
       <c r="AO5" t="n">
-        <v>109020</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+        <v>11216344</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>445934</v>
+      </c>
       <c r="AR5" t="n">
-        <v>109020</v>
+        <v>10770411</v>
       </c>
       <c r="AS5" t="n">
-        <v>-835149</v>
+        <v>-982911</v>
       </c>
       <c r="AT5" t="n">
-        <v>944169</v>
+        <v>11753322</v>
       </c>
       <c r="AU5" t="n">
-        <v>79947</v>
+        <v>10743380</v>
       </c>
       <c r="AV5" t="n">
-        <v>864222</v>
+        <v>1009942</v>
       </c>
       <c r="AW5" t="n">
-        <v>7129760</v>
+        <v>1654377</v>
       </c>
       <c r="AX5" t="n">
-        <v>34185</v>
+        <v>86380</v>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>63817</v>
+        <v>96831</v>
       </c>
       <c r="BA5" t="n">
-        <v>63817</v>
+        <v>96831</v>
       </c>
       <c r="BB5" t="n">
-        <v>168308</v>
+        <v>131170</v>
       </c>
       <c r="BC5" t="n">
-        <v>799358</v>
+        <v>247364</v>
       </c>
       <c r="BD5" t="n">
-        <v>-357355</v>
+        <v>-580102</v>
       </c>
       <c r="BE5" t="n">
-        <v>1156713</v>
+        <v>827466</v>
       </c>
       <c r="BF5" t="n">
-        <v>6064092</v>
+        <v>1092632</v>
       </c>
       <c r="BG5" t="n">
-        <v>5691673</v>
+        <v>671812</v>
       </c>
       <c r="BH5" t="n">
-        <v>372419</v>
+        <v>420820</v>
       </c>
       <c r="BI5" t="n">
-        <v>372419</v>
+        <v>420820</v>
       </c>
     </row>
   </sheetData>
@@ -2369,424 +2369,424 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-8638199</v>
+        <v>-6258990</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>-11633</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>-204436487</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7163881</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>-5583340</v>
-      </c>
-      <c r="H2" t="n">
-        <v>195390</v>
-      </c>
+        <v>-996055</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>430063</v>
+        <v>381846</v>
       </c>
       <c r="J2" t="n">
-        <v>7936460</v>
+        <v>2308386</v>
       </c>
       <c r="K2" t="n">
-        <v>-2485</v>
+        <v>57790</v>
       </c>
       <c r="L2" t="n">
-        <v>-7503912</v>
+        <v>-1984330</v>
       </c>
       <c r="M2" t="n">
-        <v>-86818</v>
+        <v>-198144728</v>
       </c>
       <c r="N2" t="n">
-        <v>-86818</v>
+        <v>-198144728</v>
       </c>
       <c r="O2" t="n">
-        <v>-150370</v>
+        <v>-1004882</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-11633</v>
+        <v>-197272606</v>
       </c>
       <c r="T2" t="n">
-        <v>-11633</v>
+        <v>-197272606</v>
       </c>
       <c r="U2" t="n">
-        <v>-11633</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>-204436487</v>
+      </c>
+      <c r="V2" t="n">
+        <v>7163881</v>
+      </c>
       <c r="W2" t="n">
-        <v>-4362235</v>
+        <v>201423333</v>
       </c>
       <c r="X2" t="n">
-        <v>-4362235</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-24182</v>
-      </c>
+        <v>201423333</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>-24182</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>202419388</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>202419388</v>
+      </c>
       <c r="AD2" t="n">
-        <v>1156252</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1245287</v>
-      </c>
+        <v>-696271</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-89035</v>
+        <v>-696271</v>
       </c>
       <c r="AG2" t="n">
-        <v>-5494305</v>
+        <v>-299784</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3054859</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>-195390</v>
-      </c>
+        <v>-5262935</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>192</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-3526401</v>
+        <v>-54993396</v>
       </c>
       <c r="AL2" t="n">
-        <v>-3526401</v>
+        <v>-54993396</v>
       </c>
       <c r="AM2" t="n">
-        <v>666932</v>
+        <v>49730269</v>
       </c>
       <c r="AN2" t="n">
-        <v>21044</v>
+        <v>725403</v>
       </c>
       <c r="AO2" t="n">
-        <v>645888</v>
+        <v>49004866</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-4492507</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-412500</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+        <v>-4729625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>200000</v>
+      </c>
       <c r="F3" t="n">
-        <v>8550000</v>
+        <v>8524747</v>
       </c>
       <c r="G3" t="n">
-        <v>-2661777</v>
+        <v>-1771388</v>
       </c>
       <c r="H3" t="n">
-        <v>288811</v>
+        <v>262042</v>
       </c>
       <c r="I3" t="n">
-        <v>7936460</v>
+        <v>4262328</v>
       </c>
       <c r="J3" t="n">
-        <v>4262328</v>
+        <v>380845</v>
       </c>
       <c r="K3" t="n">
-        <v>59677</v>
+        <v>98006</v>
       </c>
       <c r="L3" t="n">
-        <v>3614455</v>
+        <v>3783477</v>
       </c>
       <c r="M3" t="n">
-        <v>8104569</v>
+        <v>8018205</v>
       </c>
       <c r="N3" t="n">
-        <v>8104569</v>
+        <v>8018205</v>
       </c>
       <c r="O3" t="n">
-        <v>-65862</v>
+        <v>-13084</v>
       </c>
       <c r="P3" t="n">
-        <v>8137500</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-412500</v>
-      </c>
+        <v>8524747</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>8550000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+        <v>8524747</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-500000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-500000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>200000</v>
+      </c>
       <c r="W3" t="n">
-        <v>-2659384</v>
+        <v>-1276491</v>
       </c>
       <c r="X3" t="n">
-        <v>-2659384</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+        <v>-1276491</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>408085</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>437380</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-29295</v>
+      </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-64697</v>
+        <v>57251</v>
       </c>
       <c r="AE3" t="n">
-        <v>2393</v>
+        <v>86812</v>
       </c>
       <c r="AF3" t="n">
-        <v>-67090</v>
+        <v>-29561</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2594687</v>
+        <v>-1741827</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1830730</v>
+        <v>-2958237</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-288811</v>
+        <v>-262042</v>
       </c>
       <c r="AK3" t="n">
-        <v>-3660920</v>
+        <v>-4241907</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3660920</v>
+        <v>-4241907</v>
       </c>
       <c r="AM3" t="n">
-        <v>2119001</v>
+        <v>1545712</v>
       </c>
       <c r="AN3" t="n">
-        <v>142554</v>
+        <v>6549</v>
       </c>
       <c r="AO3" t="n">
-        <v>1976447</v>
+        <v>1539163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-4729625</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>200000</v>
-      </c>
+        <v>-4492507</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-412500</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>8524747</v>
+        <v>8550000</v>
       </c>
       <c r="G4" t="n">
-        <v>-1771388</v>
+        <v>-2661777</v>
       </c>
       <c r="H4" t="n">
-        <v>262042</v>
+        <v>288811</v>
       </c>
       <c r="I4" t="n">
+        <v>7936460</v>
+      </c>
+      <c r="J4" t="n">
         <v>4262328</v>
       </c>
-      <c r="J4" t="n">
-        <v>380845</v>
-      </c>
       <c r="K4" t="n">
-        <v>98006</v>
+        <v>59677</v>
       </c>
       <c r="L4" t="n">
-        <v>3783477</v>
+        <v>3614455</v>
       </c>
       <c r="M4" t="n">
-        <v>8018205</v>
+        <v>8104569</v>
       </c>
       <c r="N4" t="n">
-        <v>8018205</v>
+        <v>8104569</v>
       </c>
       <c r="O4" t="n">
-        <v>-13084</v>
+        <v>-65862</v>
       </c>
       <c r="P4" t="n">
-        <v>8524747</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>8137500</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-412500</v>
+      </c>
       <c r="R4" t="n">
-        <v>8524747</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-500000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-500000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>200000</v>
-      </c>
+        <v>8550000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-1276491</v>
+        <v>-2659384</v>
       </c>
       <c r="X4" t="n">
-        <v>-1276491</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>408085</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>437380</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-29295</v>
-      </c>
+        <v>-2659384</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>57251</v>
+        <v>-64697</v>
       </c>
       <c r="AE4" t="n">
-        <v>86812</v>
+        <v>2393</v>
       </c>
       <c r="AF4" t="n">
-        <v>-29561</v>
+        <v>-67090</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1741827</v>
+        <v>-2594687</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2958237</v>
+        <v>-1830730</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-262042</v>
+        <v>-288811</v>
       </c>
       <c r="AK4" t="n">
-        <v>-4241907</v>
+        <v>-3660920</v>
       </c>
       <c r="AL4" t="n">
-        <v>-4241907</v>
+        <v>-3660920</v>
       </c>
       <c r="AM4" t="n">
-        <v>1545712</v>
+        <v>2119001</v>
       </c>
       <c r="AN4" t="n">
-        <v>6549</v>
+        <v>142554</v>
       </c>
       <c r="AO4" t="n">
-        <v>1539163</v>
+        <v>1976447</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-6258990</v>
+        <v>-8638199</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-204436487</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7163881</v>
-      </c>
+        <v>-11633</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-996055</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>-5583340</v>
+      </c>
+      <c r="H5" t="n">
+        <v>195390</v>
+      </c>
       <c r="I5" t="n">
-        <v>381846</v>
+        <v>430063</v>
       </c>
       <c r="J5" t="n">
-        <v>2308386</v>
+        <v>7936460</v>
       </c>
       <c r="K5" t="n">
-        <v>57790</v>
+        <v>-2485</v>
       </c>
       <c r="L5" t="n">
-        <v>-1984330</v>
+        <v>-7503912</v>
       </c>
       <c r="M5" t="n">
-        <v>-198144728</v>
+        <v>-86818</v>
       </c>
       <c r="N5" t="n">
-        <v>-198144728</v>
+        <v>-86818</v>
       </c>
       <c r="O5" t="n">
-        <v>-1004882</v>
+        <v>-150370</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-197272606</v>
+        <v>-11633</v>
       </c>
       <c r="T5" t="n">
-        <v>-197272606</v>
+        <v>-11633</v>
       </c>
       <c r="U5" t="n">
-        <v>-204436487</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7163881</v>
-      </c>
+        <v>-11633</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>201423333</v>
+        <v>-4362235</v>
       </c>
       <c r="X5" t="n">
-        <v>201423333</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+        <v>-4362235</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-24182</v>
+      </c>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>202419388</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>202419388</v>
-      </c>
+      <c r="AA5" t="n">
+        <v>-24182</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-696271</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>1156252</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1245287</v>
+      </c>
       <c r="AF5" t="n">
-        <v>-696271</v>
+        <v>-89035</v>
       </c>
       <c r="AG5" t="n">
-        <v>-299784</v>
+        <v>-5494305</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5262935</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>192</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-3054859</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>-195390</v>
+      </c>
       <c r="AK5" t="n">
-        <v>-54993396</v>
+        <v>-3526401</v>
       </c>
       <c r="AL5" t="n">
-        <v>-54993396</v>
+        <v>-3526401</v>
       </c>
       <c r="AM5" t="n">
-        <v>49730269</v>
+        <v>666932</v>
       </c>
       <c r="AN5" t="n">
-        <v>725403</v>
+        <v>21044</v>
       </c>
       <c r="AO5" t="n">
-        <v>49004866</v>
+        <v>645888</v>
       </c>
     </row>
   </sheetData>
@@ -3351,197 +3351,197 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
       <c r="ES1" t="inlineStr">
@@ -3571,10 +3571,8 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
+      <c r="E2" t="n">
+        <v>6005</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3652,7 +3650,7 @@
         <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="X2" t="n">
         <v>1767139200</v>
@@ -3669,28 +3667,28 @@
         <v>4</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="AD2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.026</v>
       </c>
-      <c r="AE2" t="n">
-        <v>0.029</v>
-      </c>
       <c r="AF2" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
       <c r="AH2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.026</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.029</v>
       </c>
       <c r="AJ2" t="n">
         <v>1038182400</v>
@@ -3699,34 +3697,34 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.242</v>
+        <v>0.208</v>
       </c>
       <c r="AM2" t="n">
-        <v>548375</v>
+        <v>353942</v>
       </c>
       <c r="AN2" t="n">
-        <v>548375</v>
+        <v>353942</v>
       </c>
       <c r="AO2" t="n">
-        <v>427595</v>
+        <v>495777</v>
       </c>
       <c r="AP2" t="n">
-        <v>377918</v>
+        <v>669358</v>
       </c>
       <c r="AQ2" t="n">
-        <v>377918</v>
+        <v>669358</v>
       </c>
       <c r="AR2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0.026</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0.027</v>
-      </c>
       <c r="AT2" t="n">
-        <v>10602904</v>
+        <v>10195100</v>
       </c>
       <c r="AU2" t="n">
-        <v>11826315</v>
+        <v>10195099</v>
       </c>
       <c r="AV2" t="n">
         <v>0.014</v>
@@ -3741,13 +3739,13 @@
         <v>0.014</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.040556</v>
+        <v>15.423612</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.02887</v>
+        <v>0.02806</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0337575</v>
+        <v>0.034415</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
@@ -3764,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>14168441</v>
+        <v>12694725</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -3788,7 +3786,7 @@
         <v>0.021</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.2380953</v>
+        <v>1.1904762</v>
       </c>
       <c r="BP2" t="n">
         <v>1751241600</v>
@@ -3814,16 +3812,16 @@
         <v>1720137600</v>
       </c>
       <c r="BW2" t="n">
-        <v>21.435</v>
+        <v>19.205</v>
       </c>
       <c r="BX2" t="n">
-        <v>-5.383</v>
+        <v>-4.823</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.61111116</v>
+        <v>0.4705882</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="CA2" t="n">
         <v>0.13114</v>
@@ -3837,7 +3835,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -3936,150 +3934,150 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DF2" t="n">
-        <v>1758711540</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>1759147200</v>
-      </c>
-      <c r="DH2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.002869999</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.09941112000000001</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.0077575</v>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Morella Corporation Limited</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>1782107881</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>finmb_7652812</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Australia/Sydney</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>AEST</t>
+        </is>
       </c>
       <c r="DM2" t="n">
-        <v>-0.22980078</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>20</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>20</v>
+        <v>36000000</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>au_market</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>Altura Mining Limited</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DR2" t="b">
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
         <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.025</v>
       </c>
       <c r="DS2" t="b">
         <v>0</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>MORELLA FPO [1MC]</t>
+        </is>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
         <v>978908400000</v>
       </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>POSTPOST</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>MORELLA FPO [1MC]</t>
-        </is>
-      </c>
       <c r="DW2" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="DX2" t="b">
         <v>0</v>
       </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>0.025 - 0.026</t>
+        </is>
+      </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="DZ2" t="n">
-        <v>1780464001</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>finmb_7652812</t>
-        </is>
+        <v>495777</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.78571427</v>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>Australia/Sydney</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>AEST</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>au_market</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>Morella Corporation Limited</t>
-        </is>
+          <t>0.014 - 0.11</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.7727273</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>47.058823</v>
       </c>
       <c r="EG2" t="n">
-        <v>-10.344824</v>
+        <v>1758711540</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.0029999986</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>0.026 - 0.029</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>ASX</t>
-        </is>
+        <v>1759147200</v>
+      </c>
+      <c r="EI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.00306</v>
       </c>
       <c r="EL2" t="n">
-        <v>427595</v>
+        <v>-0.10905203</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.012</v>
+        <v>-0.009414999</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.85714287</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>0.014 - 0.11</t>
-        </is>
+        <v>-0.27357253</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>20</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.08400000000000001</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.76363635</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>61.111115</v>
+        <v>20</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>Altura Mining Limited</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
       </c>
       <c r="ES2" t="inlineStr"/>
     </row>
